--- a/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>AAME</t>
   </si>
@@ -656,225 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E8" s="3">
         <v>49200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>44700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>51600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>59900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>52300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>47700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>43100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>55000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>49200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>46400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>49400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>40500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>48800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>44800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>43600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>43900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>40000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,97 +1496,101 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E17" s="3">
         <v>46200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>49300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>41000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>49000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>48200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>49200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>48400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>44800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>46400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>45500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>43700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>41000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>43800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>38100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,88 +1598,91 @@
         <v>3000</v>
       </c>
       <c r="E18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,111 +1816,114 @@
         <v>3200</v>
       </c>
       <c r="E21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>35000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E22" s="3">
         <v>800</v>
       </c>
       <c r="F22" s="3">
+        <v>800</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
       </c>
       <c r="J22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
@@ -1895,7 +1935,7 @@
         <v>300</v>
       </c>
       <c r="N22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
@@ -1904,7 +1944,7 @@
         <v>400</v>
       </c>
       <c r="Q22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R22" s="3">
         <v>500</v>
@@ -1934,7 +1974,7 @@
         <v>500</v>
       </c>
       <c r="AA22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB22" s="3">
         <v>400</v>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
       </c>
       <c r="X24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1200</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2535,17 +2596,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2553,12 +2614,12 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>400</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2838,97 +2908,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1200</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1200</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E41" s="3">
         <v>24200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>24500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,97 +3533,103 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E43" s="3">
         <v>30800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>15600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>12600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3710,8 +3809,11 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,157 +3901,163 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>220800</v>
+      </c>
+      <c r="E47" s="3">
         <v>227900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>235600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>228700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>224400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>243900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>264800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>283400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>285900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>286000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>271100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>279300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>274600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>266900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>241200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>268600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>247400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>254400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>253700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>241900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>245000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>246700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>245800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>247500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>252100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>240600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>244400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>244100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>4800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3959,8 +4067,8 @@
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>2500</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E52" s="3">
         <v>15100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
-      </c>
-      <c r="K52" s="3">
-        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
       </c>
       <c r="M52" s="3">
+        <v>300</v>
+      </c>
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2300</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
@@ -4328,13 +4448,16 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>200</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E54" s="3">
         <v>373000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>353600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>367100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>360300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>379300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>375000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>402300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>404100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>404500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>383100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>405200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>385000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>385700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>347900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>377600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>383300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>371700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>354200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>344300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>339500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>341700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>325800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>343200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>334300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>332700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>312900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>318600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>321500</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4666,8 +4797,11 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4755,97 +4889,103 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>141300</v>
+      </c>
+      <c r="E59" s="3">
         <v>148200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>143600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>142600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>150200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>129300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>139900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>142500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>140000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>127100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>134200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>131500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>136200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>120600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>133000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>140500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>133100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>118200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>118900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>115300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>119000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>106000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>113500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>110100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>113500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>95200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>104500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>102300</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4933,28 +5073,31 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>36700</v>
+        <v>36800</v>
       </c>
       <c r="E61" s="3">
         <v>36700</v>
       </c>
       <c r="F61" s="3">
+        <v>36700</v>
+      </c>
+      <c r="G61" s="3">
         <v>35700</v>
-      </c>
-      <c r="G61" s="3">
-        <v>34700</v>
       </c>
       <c r="H61" s="3">
         <v>34700</v>
       </c>
       <c r="I61" s="3">
-        <v>33700</v>
+        <v>34700</v>
       </c>
       <c r="J61" s="3">
         <v>33700</v>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>33700</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>33700</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5054,15 +5200,15 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5078,8 +5224,8 @@
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -5094,25 +5240,28 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>900</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E66" s="3">
         <v>269500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>249200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>264900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>262400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>270200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>248600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>261000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>264100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>262100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>249900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>260100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>256900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>261800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>246300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>259200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>266900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>259000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>242800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>242900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>237400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>240000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>224100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>230300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>224800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>225200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>205900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>213100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E72" s="3">
         <v>52000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>50400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>52000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>51000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>51800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>48700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>49700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>46900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>47800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>36000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>34300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>27800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>34900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>40900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>28600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>26500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E76" s="3">
         <v>103400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>104300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>102100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>97900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>109000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>126400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>141200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>139900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>142300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>133200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>145000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>128000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>123800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>101500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>118300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>116400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>112700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>111400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>101300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>102100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>101600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>101700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>112900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>109500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>107500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>106900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>105500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1200</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6630,22 +6829,22 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>23200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>19600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
@@ -6654,49 +6853,52 @@
         <v>300</v>
       </c>
       <c r="R83" s="3">
+        <v>300</v>
+      </c>
+      <c r="S83" s="3">
         <v>17700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E89" s="3">
         <v>6700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7271,20 +7492,20 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -7304,11 +7525,11 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -7328,11 +7549,11 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -7343,7 +7564,7 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>24900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>11800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>2100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>3700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,13 +7884,14 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>10700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4000</v>
-      </c>
-      <c r="V102" s="3">
-        <v>2600</v>
       </c>
       <c r="W102" s="3">
         <v>2600</v>
       </c>
       <c r="X102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>15100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>AAME</t>
   </si>
@@ -656,232 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F8" s="3">
         <v>44600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>49200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>46300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>45200</v>
       </c>
       <c r="H8" s="3">
         <v>46300</v>
       </c>
       <c r="I8" s="3">
+        <v>45200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K8" s="3">
         <v>44700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>51600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>49700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>49300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>51500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>49100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>59900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>46300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>49700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>39400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>52300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>47700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>43100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>55000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>49200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>46400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>49400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>40500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>48800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>44800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>43600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>43900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>40000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F17" s="3">
         <v>41600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>46200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>47300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>43200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>46800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>46400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>47500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>46000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>50200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>47400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>49300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>44600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>43500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>41000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>49200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>50100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>49000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>48200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>49200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>48400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>44800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>44900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>46400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>45500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>43700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>41000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>43800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>38100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F18" s="3">
         <v>3000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>15300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>8700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>1900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1807,100 +1874,112 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F21" s="3">
         <v>3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>26900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>35000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>8900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-9500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>19800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-4900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>9600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>4600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>7400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>5600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>5700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>3800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>7300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1908,28 +1987,28 @@
         <v>900</v>
       </c>
       <c r="E22" s="3">
+        <v>900</v>
+      </c>
+      <c r="F22" s="3">
+        <v>900</v>
+      </c>
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
@@ -1938,19 +2017,19 @@
         <v>300</v>
       </c>
       <c r="O22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
       </c>
       <c r="R22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T22" s="3">
         <v>500</v>
@@ -1977,10 +2056,10 @@
         <v>500</v>
       </c>
       <c r="AB22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AC22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD22" s="3">
         <v>400</v>
@@ -1991,177 +2070,189 @@
       <c r="AF22" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F23" s="3">
         <v>2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>15000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>8300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-10200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>4000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>1500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-100</v>
       </c>
       <c r="AC24" s="3">
         <v>700</v>
@@ -2170,13 +2261,19 @@
         <v>-100</v>
       </c>
       <c r="AE24" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>11800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>6500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-4400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>4200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>2100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>11700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>6400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-8200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>2000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1200</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,33 +2720,33 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>11700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>6400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-8200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>2400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>1200</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>11700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>6400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-8200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>2400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>1200</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>28300</v>
+      </c>
+      <c r="F41" s="3">
         <v>23900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>24200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>13500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>28900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>15600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>24800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>20400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>19300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>16400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>8300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>12900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>36000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>11500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>12600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>10000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>7500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>24500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>9500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>12600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>10700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>13300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3715,112 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F43" s="3">
         <v>24700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>30800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>11600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>15400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>21900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>29100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>15000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>22500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>29500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>9900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>27500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>20000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>23800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>10800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>13100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>18000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>23900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>12100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>15200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>15000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>19400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>7900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>13200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>15600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>25000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>7200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>12600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3911,14 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +4009,14 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,177 +4107,189 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>237000</v>
+      </c>
+      <c r="F47" s="3">
         <v>220800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>227900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>235600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>228700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>224400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>243900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>264800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>283400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>285900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>286000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>271100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>279300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>274600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>266900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>241200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>268600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>247400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>254400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>253700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>241900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>245000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>246700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>245800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>247500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>252100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>240600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>244400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>244100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F48" s="3">
         <v>2800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>4100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>4800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>2500</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,86 +4597,92 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F52" s="3">
         <v>17200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>15100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>14200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2300</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
@@ -4451,13 +4690,19 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>200</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>365800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>381300</v>
+      </c>
+      <c r="F54" s="3">
         <v>361600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>373000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>353600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>367100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>360300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>379300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>375000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>402300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>404100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>404500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>383100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>405200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>385000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>385700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>347900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>377600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>383300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>371700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>354200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>344300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>339500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>341700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>325800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>343200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>334300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>332700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>312900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>318600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>321500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4967,10 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,8 +5061,14 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,100 +5159,112 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>144700</v>
+      </c>
+      <c r="F59" s="3">
         <v>141300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>148200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>127800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>143600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>142600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>150200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>129300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>139900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>142500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>140000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>127100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>134200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>131500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>136200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>120600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>133000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>140500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>133100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>118200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>118900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>115300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>119000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>106000</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>113500</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>110100</v>
       </c>
       <c r="AC59" s="3">
         <v>113500</v>
       </c>
       <c r="AD59" s="3">
+        <v>110100</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>113500</v>
+      </c>
+      <c r="AF59" s="3">
         <v>95200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>104500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>102300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,34 +5355,40 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E61" s="3">
         <v>36800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>36800</v>
+      </c>
+      <c r="G61" s="3">
         <v>36700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>36700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>35700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>34700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>34700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>33700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>33700</v>
       </c>
       <c r="L61" s="3">
         <v>33700</v>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>33700</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>33700</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>33700</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5203,18 +5494,18 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
         <v>1300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5227,11 +5518,11 @@
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -5243,25 +5534,31 @@
         <v>0</v>
       </c>
       <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
         <v>600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>900</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5845,14 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5545,91 +5860,97 @@
         <v>262900</v>
       </c>
       <c r="E66" s="3">
+        <v>274000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>262900</v>
+      </c>
+      <c r="G66" s="3">
         <v>269500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>249200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>264900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>262400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>270200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>248600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>261000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>264100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>262100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>249900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>260100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>256900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>261800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>246300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>259200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>266900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>259000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>242800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>242900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>237400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>240000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>224100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>230300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>224800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>225200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>205900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>213100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>50900</v>
+      </c>
+      <c r="F72" s="3">
         <v>53300</v>
-      </c>
-      <c r="E72" s="3">
-        <v>52000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>50400</v>
       </c>
       <c r="G72" s="3">
         <v>52000</v>
       </c>
       <c r="H72" s="3">
+        <v>50400</v>
+      </c>
+      <c r="I72" s="3">
+        <v>52000</v>
+      </c>
+      <c r="J72" s="3">
         <v>51000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>51800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>53600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>51300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>48700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>49700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>46900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>47800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>36000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>34300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>27800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>36000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>34900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>36300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>40900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>37200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>37100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>36300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>33200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>31000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>28600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>27900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>26500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>27300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>107200</v>
+      </c>
+      <c r="F76" s="3">
         <v>98700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>103400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>104300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>102100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>97900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>109000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>126400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>141200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>139900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>142300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>133200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>145000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>128000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>123800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>101500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>118300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>116400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>112700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>111400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>101300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>102100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>101600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>101700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>112900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>109500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>107500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>106900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>105500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>11700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>6400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-8200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>2400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>1200</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,16 +7200,18 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -6832,73 +7229,79 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>23200</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>23200</v>
+      </c>
+      <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
         <v>-100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>19600</v>
-      </c>
-      <c r="P83" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>17700</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
       </c>
       <c r="U83" s="3">
+        <v>17700</v>
+      </c>
+      <c r="V83" s="3">
+        <v>300</v>
+      </c>
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>8800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>3000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>4000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>3000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>3100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>3800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>5500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F89" s="3">
         <v>1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-11600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>8700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>9900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>11100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-10500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>5800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-6900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>9600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>3700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>4600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>3600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7495,23 +7936,23 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -7528,14 +7969,14 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -7552,14 +7993,14 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -7567,16 +8008,22 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>4000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>7200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>6000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-28500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>24900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-6500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>11800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>2100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>3700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,20 +8350,22 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-400</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,67 +8738,73 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>1000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>600</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
-        <v>-400</v>
+        <v>600</v>
       </c>
       <c r="L100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>-400</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>-400</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-500</v>
-      </c>
       <c r="V100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W100" s="3">
         <v>-500</v>
@@ -8322,22 +8813,22 @@
         <v>-100</v>
       </c>
       <c r="Y100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-300</v>
       </c>
       <c r="AC100" s="3">
         <v>-500</v>
       </c>
       <c r="AD100" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AE100" s="3">
         <v>-500</v>
@@ -8345,8 +8836,14 @@
       <c r="AF100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>10700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-15300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>10400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-10900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>8000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-4600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-23100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>24600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-4000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>2600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>15100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>AAME</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E8" s="3">
         <v>47000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>46300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>44700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>51500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>59900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>49700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>52300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>47700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>43100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>55000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>49200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>46400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>49400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>40500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>48800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>44800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>43600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>43900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>40000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E17" s="3">
         <v>48600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>49000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>44600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>41000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>49200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>50100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>49000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>48200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>49200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>48400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>44800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>44900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>46400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>45500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>43700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>41000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>43800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>38100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3000</v>
       </c>
       <c r="G18" s="3">
         <v>3000</v>
       </c>
       <c r="H18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1880,106 +1914,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>3200</v>
       </c>
       <c r="G21" s="3">
         <v>3200</v>
       </c>
       <c r="H21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>19800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1993,25 +2033,25 @@
         <v>900</v>
       </c>
       <c r="G22" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H22" s="3">
         <v>800</v>
       </c>
       <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
       </c>
       <c r="M22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
@@ -2023,7 +2063,7 @@
         <v>300</v>
       </c>
       <c r="Q22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R22" s="3">
         <v>400</v>
@@ -2032,7 +2072,7 @@
         <v>400</v>
       </c>
       <c r="T22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U22" s="3">
         <v>500</v>
@@ -2062,7 +2102,7 @@
         <v>500</v>
       </c>
       <c r="AD22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AE22" s="3">
         <v>400</v>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>100</v>
       </c>
       <c r="AA24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB24" s="3">
         <v>800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1200</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,17 +2787,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2744,12 +2805,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>400</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1200</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1200</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3534,97 +3621,100 @@
         <v>21200</v>
       </c>
       <c r="E41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F41" s="3">
         <v>28300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>36000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E43" s="3">
         <v>14700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>30800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>18000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>15200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>13200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>12600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,175 +4215,181 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>237000</v>
+        <v>235300</v>
       </c>
       <c r="E47" s="3">
         <v>237000</v>
       </c>
       <c r="F47" s="3">
+        <v>237000</v>
+      </c>
+      <c r="G47" s="3">
         <v>220800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>227900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>235600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>228700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>224400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>243900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>264800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>283400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>285900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>286000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>271100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>279300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>274600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>266900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>241200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>268600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>247400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>254400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>253700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>241900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>245000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>246700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>245800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>247500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>252100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>240600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>244400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>244100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>4800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4291,8 +4399,8 @@
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>2500</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,89 +4720,92 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E52" s="3">
         <v>16700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
       </c>
       <c r="P52" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2100</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2300</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
@@ -4696,13 +4816,16 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>200</v>
       </c>
-      <c r="AH52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E54" s="3">
         <v>365800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>381300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>361600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>373000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>353600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>367100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>360300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>379300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>375000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>402300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>404100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>404500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>383100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>405200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>385000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>385700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>347900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>377600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>383300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>371700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>354200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>344300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>339500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>341700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>325800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>343200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>334300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>332700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>312900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>318600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>321500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,106 +5299,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E59" s="3">
         <v>131500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>144700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>141300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>148200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>127800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>143600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>142600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>150200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>139900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>142500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>140000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>127100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>134200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>131500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>136200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>120600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>133000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>140500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>133100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>118200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>118900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>115300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>119000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>106000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>113500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>110100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>113500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>95200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>104500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>102300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5370,28 +5513,28 @@
         <v>37800</v>
       </c>
       <c r="E61" s="3">
-        <v>36800</v>
+        <v>37800</v>
       </c>
       <c r="F61" s="3">
         <v>36800</v>
       </c>
       <c r="G61" s="3">
-        <v>36700</v>
+        <v>36800</v>
       </c>
       <c r="H61" s="3">
         <v>36700</v>
       </c>
       <c r="I61" s="3">
+        <v>36700</v>
+      </c>
+      <c r="J61" s="3">
         <v>35700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>34700</v>
       </c>
       <c r="K61" s="3">
         <v>34700</v>
       </c>
       <c r="L61" s="3">
-        <v>33700</v>
+        <v>34700</v>
       </c>
       <c r="M61" s="3">
         <v>33700</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>33700</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>33700</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5500,15 +5646,15 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3">
         <v>1300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5524,8 +5670,8 @@
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -5540,25 +5686,28 @@
         <v>0</v>
       </c>
       <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>900</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>285300</v>
+      </c>
+      <c r="E66" s="3">
         <v>262900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>274000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>262900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>269500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>249200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>264900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>262400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>270200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>248600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>261000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>264100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>262100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>249900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>260100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>256900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>261800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>246300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>259200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>266900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>259000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>242800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>242900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>237400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>240000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>224100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>230300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>224800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>225200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>205900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>213100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E72" s="3">
         <v>48400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>50900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>53300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>52000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>51300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>49700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>34300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>34900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>40900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>31000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>28600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>27900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E76" s="3">
         <v>102700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>107200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>98700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>103400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>104300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>102100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>97900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>109000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>126400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>141200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>139900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>142300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>133200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>145000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>128000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>123800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>101500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>118300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>116400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>112700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>111400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>101300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>102100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>101600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>101700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>112900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>109500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>107500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>106900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>105500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1200</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7214,7 +7413,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -7235,22 +7434,22 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>23200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19600</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
@@ -7259,49 +7458,52 @@
         <v>300</v>
       </c>
       <c r="U83" s="3">
+        <v>300</v>
+      </c>
+      <c r="V83" s="3">
         <v>17700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>4000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,13 +8144,14 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7942,20 +8163,20 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -7975,11 +8196,11 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -7999,11 +8220,11 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -8014,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG91" s="3">
         <v>-100</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>7200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>6000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>24900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>11800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8364,11 +8598,11 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>-400</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-400</v>
       </c>
       <c r="F100" s="3">
         <v>-400</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-23100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>2600</v>
       </c>
       <c r="Z102" s="3">
         <v>2600</v>
       </c>
       <c r="AA102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>15100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>AAME</t>
   </si>
@@ -656,275 +656,282 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E8" s="3">
         <v>47700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>46300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>44700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>51500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>49100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>59900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>49700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>39400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>52300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>47700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>43100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>55000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>49200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>46400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>49400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>40500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>48800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>44800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>43600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>43900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>40000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>43400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>44600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>45200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>37900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>42200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>43400</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E17" s="3">
         <v>47700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>44600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>41000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>49200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>50100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>49000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>48200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>49200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>48400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>44800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>44900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>46400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>45500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>43700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>41000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>43800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>38100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>100</v>
+        <v>-1600</v>
       </c>
       <c r="E18" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>-2300</v>
+        <v>-1700</v>
       </c>
       <c r="G18" s="3">
-        <v>3000</v>
+        <v>-2200</v>
       </c>
       <c r="H18" s="3">
         <v>3000</v>
       </c>
       <c r="I18" s="3">
-        <v>-1000</v>
+        <v>3000</v>
       </c>
       <c r="J18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K18" s="3">
         <v>2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,31 +1849,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1917,109 +1951,115 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>3200</v>
       </c>
       <c r="H21" s="3">
         <v>3200</v>
       </c>
       <c r="I21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>19800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2036,25 +2076,25 @@
         <v>900</v>
       </c>
       <c r="H22" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I22" s="3">
         <v>800</v>
       </c>
       <c r="J22" s="3">
+        <v>800</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>400</v>
       </c>
       <c r="N22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -2066,7 +2106,7 @@
         <v>300</v>
       </c>
       <c r="R22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S22" s="3">
         <v>400</v>
@@ -2075,7 +2115,7 @@
         <v>400</v>
       </c>
       <c r="U22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V22" s="3">
         <v>500</v>
@@ -2105,7 +2145,7 @@
         <v>500</v>
       </c>
       <c r="AE22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AF22" s="3">
         <v>400</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>400</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
       </c>
       <c r="AB24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,17 +2851,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2808,12 +2869,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,31 +3095,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3129,109 +3199,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K33" s="3">
+        <v>900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O33" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S33" s="3">
+        <v>11700</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U33" s="3">
+        <v>6400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="W33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
-        <v>900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N33" s="3">
-        <v>2600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P33" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>11700</v>
-      </c>
-      <c r="S33" s="3">
-        <v>1800</v>
-      </c>
-      <c r="T33" s="3">
-        <v>6400</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K35" s="3">
+        <v>900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O35" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S35" s="3">
+        <v>11700</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U35" s="3">
+        <v>6400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="W35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
-        <v>900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N35" s="3">
-        <v>2600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P35" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>11700</v>
-      </c>
-      <c r="S35" s="3">
-        <v>1800</v>
-      </c>
-      <c r="T35" s="3">
-        <v>6400</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>21200</v>
+        <v>23000</v>
       </c>
       <c r="E41" s="3">
         <v>21200</v>
       </c>
       <c r="F41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="G41" s="3">
         <v>28300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>36000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,132 +3904,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E43" s="3">
         <v>34200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>18000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>23900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>15000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>13200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>20900</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>24900</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4216,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>75100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>77900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>56800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>73100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>70400</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>77300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,181 +4320,187 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>238900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>233500</v>
+      </c>
+      <c r="F47" s="3">
+        <v>235200</v>
+      </c>
+      <c r="G47" s="3">
         <v>235300</v>
       </c>
-      <c r="E47" s="3">
-        <v>237000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>237000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>220800</v>
-      </c>
       <c r="H47" s="3">
-        <v>227900</v>
+        <v>218900</v>
       </c>
       <c r="I47" s="3">
-        <v>235600</v>
+        <v>226100</v>
       </c>
       <c r="J47" s="3">
+        <v>233800</v>
+      </c>
+      <c r="K47" s="3">
         <v>228700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>224400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>243900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>264800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>283400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>285900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>286000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>271100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>279300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>274600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>266900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>241200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>268600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>247400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>254400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>253700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>241900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>245000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>246700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>245800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>247500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>252100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>240600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>244400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>244100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>4100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>4800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4402,8 +4510,8 @@
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4420,31 +4528,34 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2500</v>
+        <v>46800</v>
       </c>
       <c r="E49" s="3">
-        <v>2500</v>
+        <v>46400</v>
       </c>
       <c r="F49" s="3">
-        <v>2500</v>
+        <v>45700</v>
       </c>
       <c r="G49" s="3">
-        <v>2500</v>
+        <v>46400</v>
       </c>
       <c r="H49" s="3">
-        <v>2500</v>
+        <v>44500</v>
       </c>
       <c r="I49" s="3">
-        <v>2500</v>
+        <v>43800</v>
       </c>
       <c r="J49" s="3">
-        <v>2500</v>
+        <v>44800</v>
       </c>
       <c r="K49" s="3">
         <v>2500</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>2500</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>2500</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,92 +4840,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17200</v>
+        <v>1700</v>
       </c>
       <c r="E52" s="3">
-        <v>16700</v>
+        <v>2400</v>
       </c>
       <c r="F52" s="3">
-        <v>15700</v>
+        <v>1500</v>
       </c>
       <c r="G52" s="3">
-        <v>17200</v>
+        <v>6500</v>
       </c>
       <c r="H52" s="3">
-        <v>15100</v>
+        <v>6000</v>
       </c>
       <c r="I52" s="3">
-        <v>13700</v>
+        <v>2100</v>
       </c>
       <c r="J52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K52" s="3">
         <v>14200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>300</v>
       </c>
       <c r="Q52" s="3">
+        <v>300</v>
+      </c>
+      <c r="R52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2300</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
       <c r="AE52" s="3">
         <v>0</v>
       </c>
@@ -4819,13 +4939,16 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
         <v>200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E54" s="3">
         <v>386000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>365800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>381300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>361600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>373000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>353600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>367100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>360300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>379300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>375000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>402300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>404100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>404500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>383100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>405200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>385000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>385700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>347900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>377600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>383300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>371700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>354200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>344300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>339500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>341700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>325800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>343200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>334300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>332700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>312900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>318600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>321500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,31 +5230,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>20200</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>17800</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5201,31 +5332,34 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,132 +5436,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>152000</v>
+        <v>29000</v>
       </c>
       <c r="E59" s="3">
+        <v>38000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>31300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>30600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>37900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>19400</v>
+      </c>
+      <c r="K59" s="3">
+        <v>143600</v>
+      </c>
+      <c r="L59" s="3">
+        <v>142600</v>
+      </c>
+      <c r="M59" s="3">
+        <v>150200</v>
+      </c>
+      <c r="N59" s="3">
+        <v>129300</v>
+      </c>
+      <c r="O59" s="3">
+        <v>139900</v>
+      </c>
+      <c r="P59" s="3">
+        <v>142500</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>140000</v>
+      </c>
+      <c r="R59" s="3">
+        <v>127100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>134200</v>
+      </c>
+      <c r="T59" s="3">
         <v>131500</v>
       </c>
-      <c r="F59" s="3">
-        <v>144700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>141300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>148200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>127800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>143600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>142600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>150200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>129300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>139900</v>
-      </c>
-      <c r="O59" s="3">
-        <v>142500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>140000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>127100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>134200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>131500</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>136200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>120600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>133000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>140500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>133100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>118200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>118900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>115300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>119000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>106000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>113500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>110100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>113500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>95200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>104500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>102300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>51700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>40300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>54400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,40 +5644,43 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>37800</v>
+        <v>39600</v>
       </c>
       <c r="E61" s="3">
-        <v>37800</v>
+        <v>39600</v>
       </c>
       <c r="F61" s="3">
-        <v>36800</v>
+        <v>39500</v>
       </c>
       <c r="G61" s="3">
-        <v>36800</v>
+        <v>38500</v>
       </c>
       <c r="H61" s="3">
-        <v>36700</v>
+        <v>39500</v>
       </c>
       <c r="I61" s="3">
-        <v>36700</v>
+        <v>39400</v>
       </c>
       <c r="J61" s="3">
+        <v>39400</v>
+      </c>
+      <c r="K61" s="3">
         <v>35700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>34700</v>
       </c>
       <c r="L61" s="3">
         <v>34700</v>
       </c>
       <c r="M61" s="3">
-        <v>33700</v>
+        <v>34700</v>
       </c>
       <c r="N61" s="3">
         <v>33700</v>
@@ -5605,31 +5748,34 @@
       <c r="AI61" s="3">
         <v>33700</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>33700</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>189900</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>187200</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>183100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>181100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>171300</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>171400</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>171800</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5649,15 +5795,15 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5673,8 +5819,8 @@
       <c r="X62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -5689,25 +5835,28 @@
         <v>0</v>
       </c>
       <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
         <v>600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>900</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E66" s="3">
         <v>285300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>262900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>274000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>262900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>269500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>249200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>264900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>262400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>270200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>248600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>261000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>264100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>262100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>249900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>260100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>256900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>261800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>246300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>259200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>266900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>259000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>242800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>242900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>237400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>240000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>224100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>230300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>224800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>225200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>205900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>213100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>100</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E72" s="3">
         <v>47600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>48400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>50900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>52000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>51000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>51800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>49700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>34300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>27800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>37100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>31000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>28600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>27900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>26500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E76" s="3">
         <v>100600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>102700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>107200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>98700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>103400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>104300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>102100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>97900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>109000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>141200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>139900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>142300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>133200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>145000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>128000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>123800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>101500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>118300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>116400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>112700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>111400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>101300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>102100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>101600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>101700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>112900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>109500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>107500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>106900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>105500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K81" s="3">
+        <v>900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O81" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S81" s="3">
+        <v>11700</v>
+      </c>
+      <c r="T81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U81" s="3">
+        <v>6400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="W81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
-        <v>900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N81" s="3">
-        <v>2600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P81" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>11700</v>
-      </c>
-      <c r="S81" s="3">
-        <v>1800</v>
-      </c>
-      <c r="T81" s="3">
-        <v>6400</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,19 +7599,20 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -7437,22 +7636,22 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
         <v>23200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>19600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
@@ -7461,49 +7660,52 @@
         <v>300</v>
       </c>
       <c r="V83" s="3">
+        <v>300</v>
+      </c>
+      <c r="W83" s="3">
         <v>17700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>3100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,17 +8365,18 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -8166,20 +8387,20 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -8199,11 +8420,11 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -8223,11 +8444,11 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -8238,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>-100</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>7200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>6000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>24900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>11800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>3700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8595,22 +8829,22 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G96" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-400</v>
       </c>
       <c r="G100" s="3">
         <v>-400</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-23100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4000</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>2600</v>
       </c>
       <c r="AA102" s="3">
         <v>2600</v>
       </c>
       <c r="AB102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>15100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>AAME</t>
   </si>
@@ -656,289 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F8" s="3">
         <v>44500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>47700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>47000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>46700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>44600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>49200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>46300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>45200</v>
       </c>
       <c r="L8" s="3">
         <v>46300</v>
       </c>
       <c r="M8" s="3">
+        <v>45200</v>
+      </c>
+      <c r="N8" s="3">
+        <v>46300</v>
+      </c>
+      <c r="O8" s="3">
         <v>44700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>51600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>49700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>49300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>51500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>49100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>59900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>46300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>49700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>39400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>52300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>47700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>43100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>55000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>49200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>46400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>49400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>40500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>48800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>44800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>43600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>43900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F9" s="3">
         <v>42300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>43400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>44600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>45200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>37900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>42200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>43400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1011,38 +1024,44 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>7000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1134,14 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1178,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1284,14 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1394,14 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,11 +1426,11 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1465,8 +1504,14 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1483,19 +1528,19 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1569,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>46100</v>
+        <v>48300</v>
       </c>
       <c r="E17" s="3">
         <v>47700</v>
       </c>
       <c r="F17" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>47700</v>
+      </c>
+      <c r="H17" s="3">
         <v>48600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>49000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>41600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>46200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>47300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>43200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>46800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>46400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>47500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>46000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>50200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>47400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>49300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>44600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>43500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>41000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>49200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>50100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>49000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>48200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>49200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>48400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>44800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>44900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>46400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>45500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>43700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>41000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>43800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>4100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>15300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>8700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-9800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>2200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>2600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1915,10 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,11 +1943,11 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1954,120 +2021,132 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1500</v>
+        <v>1900</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="F21" s="3">
         <v>-1500</v>
       </c>
       <c r="G21" s="3">
+        <v>100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>26900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>35000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>8900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-9500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>19800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>6000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>9600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>7400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>5600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>4000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>5700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>3800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F22" s="3">
         <v>900</v>
@@ -2079,28 +2158,28 @@
         <v>900</v>
       </c>
       <c r="I22" s="3">
+        <v>900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>900</v>
+      </c>
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>300</v>
-      </c>
-      <c r="P22" s="3">
-        <v>300</v>
       </c>
       <c r="Q22" s="3">
         <v>300</v>
@@ -2109,19 +2188,19 @@
         <v>300</v>
       </c>
       <c r="S22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U22" s="3">
         <v>400</v>
       </c>
       <c r="V22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X22" s="3">
         <v>500</v>
@@ -2148,10 +2227,10 @@
         <v>500</v>
       </c>
       <c r="AF22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AG22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AH22" s="3">
         <v>400</v>
@@ -2162,201 +2241,213 @@
       <c r="AJ22" s="3">
         <v>400</v>
       </c>
+      <c r="AK22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2500</v>
+        <v>1000</v>
       </c>
       <c r="E23" s="3">
-        <v>-800</v>
+        <v>500</v>
       </c>
       <c r="F23" s="3">
         <v>-2500</v>
       </c>
       <c r="G23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>15000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-10200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>5300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-500</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>-500</v>
       </c>
       <c r="G24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>700</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>-100</v>
       </c>
       <c r="AG24" s="3">
         <v>700</v>
@@ -2365,13 +2456,19 @@
         <v>-100</v>
       </c>
       <c r="AI24" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2000</v>
+        <v>800</v>
       </c>
       <c r="E26" s="3">
-        <v>-700</v>
+        <v>400</v>
       </c>
       <c r="F26" s="3">
         <v>-2000</v>
       </c>
       <c r="G26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>11800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>4200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2100</v>
+        <v>700</v>
       </c>
       <c r="E27" s="3">
-        <v>-800</v>
+        <v>300</v>
       </c>
       <c r="F27" s="3">
         <v>-2100</v>
       </c>
       <c r="G27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>11700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>6400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-8200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,33 +2975,33 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3231,14 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,11 +3263,11 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3202,112 +3341,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2000</v>
+        <v>800</v>
       </c>
       <c r="E33" s="3">
-        <v>-700</v>
+        <v>400</v>
       </c>
       <c r="F33" s="3">
         <v>-2000</v>
       </c>
       <c r="G33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>11700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>6400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-8200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>3100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2000</v>
+        <v>800</v>
       </c>
       <c r="E35" s="3">
-        <v>-700</v>
+        <v>400</v>
       </c>
       <c r="F35" s="3">
         <v>-2000</v>
       </c>
       <c r="G35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>11700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>6400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-8200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>3100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F41" s="3">
         <v>23000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>21200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>21200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>28300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>23900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>24200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>13500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>28900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>21900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>24800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>14300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>20400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>19300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>16400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>12900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>36000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>11500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>12600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>10000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>7500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>8400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>24500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>9500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>12600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>10700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,112 +4086,124 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>27500</v>
+      </c>
+      <c r="F43" s="3">
         <v>30500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>34200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>23700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>24700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>30800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>15400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>21900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>29100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>11600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>15000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>22500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>29500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>9900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>27500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>20000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>23800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>10800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>13100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>18000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>23900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>12100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>15200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>15000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>19400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>7900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>13200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>15600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>25000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>7200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,11 +4228,11 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4115,38 +4306,44 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F45" s="3">
         <v>21600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>22500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>20900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>21100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>21800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>22300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>24900</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4219,38 +4416,44 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>86000</v>
+      </c>
+      <c r="F46" s="3">
         <v>75100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>77900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>56800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>73100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>70400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>77300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>50000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4323,201 +4526,213 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>230800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>228400</v>
+      </c>
+      <c r="F47" s="3">
         <v>238900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>233500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>235200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>235300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>218900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>226100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>233800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>228700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>224400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>243900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>264800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>283400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>285900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>286000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>271100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>279300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>274600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>266900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>241200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>268600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>247400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>254400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>253700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>241900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>245000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>246700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>245800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>247500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>252100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>240600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>244400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>244100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F48" s="3">
         <v>2000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>4100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>4800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
@@ -4531,37 +4746,43 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>47400</v>
+      </c>
+      <c r="F49" s="3">
         <v>46800</v>
-      </c>
-      <c r="E49" s="3">
-        <v>46400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>45700</v>
       </c>
       <c r="G49" s="3">
         <v>46400</v>
       </c>
       <c r="H49" s="3">
+        <v>45700</v>
+      </c>
+      <c r="I49" s="3">
+        <v>46400</v>
+      </c>
+      <c r="J49" s="3">
         <v>44500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>43800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>44800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2500</v>
       </c>
       <c r="M49" s="3">
         <v>2500</v>
@@ -4635,8 +4856,14 @@
       <c r="AJ49" s="3">
         <v>2500</v>
       </c>
+      <c r="AK49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>2500</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,98 +5076,104 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J52" s="3">
         <v>6000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>6200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>14200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>14600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>11200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>3100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2300</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
       <c r="AG52" s="3">
         <v>0</v>
       </c>
@@ -4942,13 +5181,19 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
         <v>200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>388400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>393400</v>
+      </c>
+      <c r="F54" s="3">
         <v>387000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>386000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>365800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>381300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>361600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>373000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>353600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>367100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>360300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>379300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>375000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>402300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>404100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>404500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>383100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>405200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>385000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>385700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>347900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>377600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>383300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>371700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>354200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>344300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>339500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>341700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>325800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>343200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>334300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>332700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>312900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>318600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>321500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,38 +5490,40 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F57" s="3">
         <v>22500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>20000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>18800</v>
       </c>
-      <c r="G57" s="3">
-        <v>22000</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>24800</v>
+      </c>
+      <c r="J57" s="3">
         <v>21100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>20200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>17800</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5335,38 +5596,44 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5439,142 +5706,154 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>31200</v>
+      </c>
+      <c r="F59" s="3">
         <v>29000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>38000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>20700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>31300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>30600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>37900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>19400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>143600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>142600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>150200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>129300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>139900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>142500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>140000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>127100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>134200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>131500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>136200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>120600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>133000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>140500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>133100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>118200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>118900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>115300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>119000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>106000</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>113500</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>110100</v>
       </c>
       <c r="AG59" s="3">
         <v>113500</v>
       </c>
       <c r="AH59" s="3">
+        <v>110100</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>113500</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>95200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>104500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>102300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F60" s="3">
         <v>51700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>58500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>40300</v>
       </c>
-      <c r="G60" s="3">
-        <v>54400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>56100</v>
+      </c>
+      <c r="J60" s="3">
         <v>52000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>58600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>38000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5647,46 +5926,52 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F61" s="3">
         <v>39600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>39600</v>
-      </c>
-      <c r="F61" s="3">
-        <v>39500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>38500</v>
       </c>
       <c r="H61" s="3">
         <v>39500</v>
       </c>
       <c r="I61" s="3">
+        <v>36800</v>
+      </c>
+      <c r="J61" s="3">
+        <v>39500</v>
+      </c>
+      <c r="K61" s="3">
         <v>39400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>39400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>35700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>34700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>34700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>33700</v>
-      </c>
-      <c r="O61" s="3">
-        <v>33700</v>
       </c>
       <c r="P61" s="3">
         <v>33700</v>
@@ -5751,38 +6036,44 @@
       <c r="AJ61" s="3">
         <v>33700</v>
       </c>
+      <c r="AK61" s="3">
+        <v>33700</v>
+      </c>
+      <c r="AL61" s="3">
+        <v>33700</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>193900</v>
+      </c>
+      <c r="F62" s="3">
         <v>189900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>187200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>183100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>181100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>171300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>171400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>171800</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5798,18 +6089,18 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5822,11 +6113,11 @@
       <c r="Y62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5838,25 +6129,31 @@
         <v>0</v>
       </c>
       <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
         <v>600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>900</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>293800</v>
+      </c>
+      <c r="F66" s="3">
         <v>281200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>285300</v>
-      </c>
-      <c r="F66" s="3">
-        <v>262900</v>
-      </c>
-      <c r="G66" s="3">
-        <v>274000</v>
       </c>
       <c r="H66" s="3">
         <v>262900</v>
       </c>
       <c r="I66" s="3">
+        <v>274000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>262900</v>
+      </c>
+      <c r="K66" s="3">
         <v>269500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>249200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>264900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>262400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>270200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>248600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>261000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>264100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>262100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>249900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>260100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>256900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>261800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>246300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>259200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>266900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>259000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>242800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>242900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>237400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>240000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>224100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>230300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>224800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>225200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>205900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>213100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>100</v>
       </c>
+      <c r="AK70" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>45900</v>
+      </c>
+      <c r="F72" s="3">
         <v>45500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>47600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>48400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>50900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>53300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>52000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>50400</v>
       </c>
       <c r="K72" s="3">
         <v>52000</v>
       </c>
       <c r="L72" s="3">
+        <v>50400</v>
+      </c>
+      <c r="M72" s="3">
+        <v>52000</v>
+      </c>
+      <c r="N72" s="3">
         <v>51000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>51800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>53600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>51300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>48700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>49700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>46900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>47800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>36000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>34300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>27800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>36000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>34900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>36300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>40900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>37200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>37100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>36300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>33200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>31000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>28600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>27900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>26500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>27300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>99600</v>
+      </c>
+      <c r="F76" s="3">
         <v>105700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>100600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>102700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>107200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>98700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>103400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>104300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>102100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>97900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>109000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>126400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>141200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>139900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>142300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>133200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>145000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>128000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>123800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>101500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>118300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>116400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>112700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>111400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>101300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>102100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>101600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>101700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>112900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>109500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>107500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>106900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>105500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2000</v>
+        <v>800</v>
       </c>
       <c r="E81" s="3">
-        <v>-700</v>
+        <v>400</v>
       </c>
       <c r="F81" s="3">
         <v>-2000</v>
       </c>
       <c r="G81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>11700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>6400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-8200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>3100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,16 +7995,18 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -7639,73 +8036,79 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>23200</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>23200</v>
+      </c>
+      <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>-100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>19600</v>
-      </c>
-      <c r="T83" s="3">
-        <v>300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>300</v>
       </c>
       <c r="W83" s="3">
-        <v>17700</v>
+        <v>300</v>
       </c>
       <c r="X83" s="3">
         <v>300</v>
       </c>
       <c r="Y83" s="3">
+        <v>17700</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>8800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>3000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>2800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>4000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>2200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>3000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>3100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>3800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>6700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-11600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>8700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-8000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-6000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>9900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>11100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-10500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>5800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>9600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>3700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>4600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,13 +8805,15 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -8381,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -8390,23 +8831,23 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -8423,14 +8864,14 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -8447,14 +8888,14 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
@@ -8462,16 +8903,22 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
       </c>
+      <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +9131,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F94" s="3">
         <v>1700</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>4000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>7200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>6000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-28500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>24900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>3600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>3000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>11800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>2100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>3700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,37 +9285,39 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>400</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>400</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9721,14 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9248,67 +9739,67 @@
         <v>-400</v>
       </c>
       <c r="F100" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>-400</v>
       </c>
       <c r="H100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>1000</v>
-      </c>
-      <c r="K100" s="3">
-        <v>600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>600</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>-400</v>
+        <v>600</v>
       </c>
       <c r="P100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
         <v>-400</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S100" s="3">
         <v>-400</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-500</v>
-      </c>
       <c r="Z100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>-500</v>
@@ -9317,22 +9808,22 @@
         <v>-100</v>
       </c>
       <c r="AC100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-300</v>
       </c>
       <c r="AG100" s="3">
         <v>-500</v>
       </c>
       <c r="AH100" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AI100" s="3">
         <v>-500</v>
@@ -9340,8 +9831,14 @@
       <c r="AJ100" s="3">
         <v>-100</v>
       </c>
+      <c r="AK100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AL100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,11 +9863,11 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9444,108 +9941,120 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-7100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>4400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>10700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-9100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-10900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>10400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-7400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-4600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-23100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>24600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>2800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>2600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>15100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>2000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-2100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AAME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>AAME</t>
   </si>
@@ -656,305 +656,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E8" s="3">
         <v>50100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>49000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>47000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>44600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>46300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>44700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>51600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>49700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>49300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>51500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>49100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>59900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>46300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>49700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>39400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>52300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>47700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>43100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>55000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>49200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>46400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>49400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>40500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>48800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>44800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>43600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>43900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>40000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>43600</v>
+        <v>46500</v>
       </c>
       <c r="E9" s="3">
         <v>43600</v>
       </c>
       <c r="F9" s="3">
+        <v>43600</v>
+      </c>
+      <c r="G9" s="3">
         <v>42300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>44600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>37900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43400</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1030,41 +1037,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E10" s="3">
         <v>6500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1534,7 +1557,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
@@ -1543,7 +1566,7 @@
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E17" s="3">
         <v>48300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>46100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>46000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>49300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>44600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>41000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>49200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>50100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>49000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>48200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>49200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>48400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>44800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>44900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>46400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>45500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>43700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>41000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>43800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>38100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>3000</v>
       </c>
       <c r="K18" s="3">
         <v>3000</v>
       </c>
       <c r="L18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,8 +1983,8 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -2027,118 +2061,124 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>3200</v>
       </c>
       <c r="K21" s="3">
         <v>3200</v>
       </c>
       <c r="L21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>35000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>19800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>7300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2149,7 +2189,7 @@
         <v>800</v>
       </c>
       <c r="F22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G22" s="3">
         <v>900</v>
@@ -2164,25 +2204,25 @@
         <v>900</v>
       </c>
       <c r="K22" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L22" s="3">
         <v>800</v>
       </c>
       <c r="M22" s="3">
+        <v>800</v>
+      </c>
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
       </c>
       <c r="Q22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R22" s="3">
         <v>300</v>
@@ -2194,7 +2234,7 @@
         <v>300</v>
       </c>
       <c r="U22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V22" s="3">
         <v>400</v>
@@ -2203,7 +2243,7 @@
         <v>400</v>
       </c>
       <c r="X22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y22" s="3">
         <v>500</v>
@@ -2233,7 +2273,7 @@
         <v>500</v>
       </c>
       <c r="AH22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AI22" s="3">
         <v>400</v>
@@ -2247,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>400</v>
       </c>
+      <c r="AM22" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>100</v>
       </c>
       <c r="AE24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>11800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2981,17 +3042,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -2999,12 +3060,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>400</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,8 +3339,8 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3347,118 +3417,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E41" s="3">
         <v>35900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>21200</v>
       </c>
       <c r="H41" s="3">
         <v>21200</v>
       </c>
       <c r="I41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="J41" s="3">
         <v>28300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>36000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,118 +4182,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E43" s="3">
         <v>19200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>29500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>18000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>23900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>15200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>13200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>15600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>12600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,41 +4408,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E45" s="3">
         <v>23800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24900</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4422,41 +4521,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E46" s="3">
         <v>78900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>86000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>77900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>77300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>50000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,199 +4634,205 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>232200</v>
+      </c>
+      <c r="E47" s="3">
         <v>230800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>228400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>238900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>233500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>235200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>235300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>218900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>226100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>233800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>228700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>224400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>243900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>264800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>283400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>285900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>286000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>271100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>279300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>274600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>266900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>241200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>268600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>247400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>254400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>253700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>241900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>245000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>246700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>245800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>247500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>252100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>240600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>244400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>244100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>4900</v>
       </c>
       <c r="E48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F48" s="3">
         <v>5200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>4100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>4800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5900</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4734,8 +4842,8 @@
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -4752,40 +4860,43 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E49" s="3">
         <v>47200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>47400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>46800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>46400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>45700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>44500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>43800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2500</v>
       </c>
       <c r="N49" s="3">
         <v>2500</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>2500</v>
       </c>
+      <c r="AM49" s="3">
+        <v>2500</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,101 +5199,104 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12500</v>
+        <v>2600</v>
       </c>
       <c r="E52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F52" s="3">
         <v>2000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>300</v>
       </c>
       <c r="T52" s="3">
+        <v>300</v>
+      </c>
+      <c r="U52" s="3">
         <v>2100</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2300</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
-      </c>
       <c r="AH52" s="3">
         <v>0</v>
       </c>
@@ -5187,13 +5307,16 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
         <v>200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>429300</v>
+      </c>
+      <c r="E54" s="3">
         <v>388400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>393400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>387000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>386000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>365800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>381300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>361600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>373000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>353600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>367100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>360300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>379300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>375000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>402300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>404100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>404500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>383100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>405200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>385000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>385700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>347900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>377600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>383300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>371700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>354200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>344300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>339500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>341700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>325800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>343200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>334300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>332700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>312900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>318600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>321500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,41 +5622,42 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>27800</v>
+        <v>24900</v>
       </c>
       <c r="E57" s="3">
+        <v>22600</v>
+      </c>
+      <c r="F57" s="3">
         <v>25600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17800</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -5602,41 +5733,44 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5712,151 +5846,157 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E59" s="3">
         <v>20900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>31300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>143600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>142600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>150200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>139900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>142500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>140000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>127100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>134200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>131500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>136200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>120600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>133000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>140500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>133100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>118200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>118900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>115300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>119000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>106000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>113500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>110100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>113500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>95200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>104500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>102300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>48700</v>
+        <v>76000</v>
       </c>
       <c r="E60" s="3">
+        <v>44400</v>
+      </c>
+      <c r="F60" s="3">
         <v>58000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>58600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,49 +6072,52 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>37800</v>
+        <v>42100</v>
       </c>
       <c r="E61" s="3">
+        <v>42000</v>
+      </c>
+      <c r="F61" s="3">
         <v>41900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>39600</v>
       </c>
       <c r="G61" s="3">
         <v>39600</v>
       </c>
       <c r="H61" s="3">
+        <v>39600</v>
+      </c>
+      <c r="I61" s="3">
         <v>39500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>39400</v>
       </c>
       <c r="L61" s="3">
         <v>39400</v>
       </c>
       <c r="M61" s="3">
+        <v>39400</v>
+      </c>
+      <c r="N61" s="3">
         <v>35700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>34700</v>
       </c>
       <c r="O61" s="3">
         <v>34700</v>
       </c>
       <c r="P61" s="3">
-        <v>33700</v>
+        <v>34700</v>
       </c>
       <c r="Q61" s="3">
         <v>33700</v>
@@ -6042,41 +6185,44 @@
       <c r="AL61" s="3">
         <v>33700</v>
       </c>
+      <c r="AM61" s="3">
+        <v>33700</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E62" s="3">
         <v>199600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>193900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>189900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>187200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>183100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>181100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>171300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>171400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>171800</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6095,15 +6241,15 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6119,8 +6265,8 @@
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -6135,25 +6281,28 @@
         <v>0</v>
       </c>
       <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
         <v>600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>900</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>323200</v>
+      </c>
+      <c r="E66" s="3">
         <v>286100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>293800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>281200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>285300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>262900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>274000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>262900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>269500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>249200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>264900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>262400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>270200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>248600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>261000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>264100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>262100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>249900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>260100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>256900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>261800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>246300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>259200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>266900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>259000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>242800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>242900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>237400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>240000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>224100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>230300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>224800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>225200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>205900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>213100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>100</v>
       </c>
+      <c r="AM70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E72" s="3">
         <v>46200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>45900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>45500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>47600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>48400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>51000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>51800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>51300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>48700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>49700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>27800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>36000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>40900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>37100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>28600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>26500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>27300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E76" s="3">
         <v>102300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>99600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>105700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>100600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>102700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>107200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>98700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>103400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>104300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>109000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>126400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>141200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>139900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>142300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>133200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>145000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>128000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>123800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>101500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>118300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>116400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>112700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>111400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>101300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>102100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>101600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>101700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>112900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>109500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>107500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>106900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>105500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8009,7 +8208,7 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -8042,22 +8241,22 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>23200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>300</v>
@@ -8066,49 +8265,52 @@
         <v>300</v>
       </c>
       <c r="Y83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>17700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,26 +9027,27 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -8837,20 +9058,20 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -8870,11 +9091,11 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -8894,11 +9115,11 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
@@ -8909,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AK91" s="3">
         <v>-100</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>-100</v>
       </c>
+      <c r="AM91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1700</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>7200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>24900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>3000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>11800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>3700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,40 +9520,41 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>400</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,118 +9970,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-400</v>
       </c>
       <c r="J100" s="3">
         <v>-400</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-23100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>24600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>2600</v>
       </c>
       <c r="AD102" s="3">
         <v>2600</v>
       </c>
       <c r="AE102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>15100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2100</v>
       </c>
     </row>
